--- a/tests/assets/golden/win32com/test_template_1_filled.xlsx
+++ b/tests/assets/golden/win32com/test_template_1_filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\xlfill\tests\assets\golden\win32com\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\fillxl\tests\assets\golden\win32com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC7F6658-6D69-4448-B631-5472F278CB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{536D528E-9360-4F28-A159-21F76458D34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,14 +186,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +527,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -545,14 +549,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -590,92 +594,92 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>0.12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>0.34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B5">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>0.78</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>0.9</v>
       </c>
     </row>
@@ -747,7 +751,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
     </row>

--- a/tests/assets/golden/win32com/test_template_1_filled.xlsx
+++ b/tests/assets/golden/win32com/test_template_1_filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\fillxl\tests\assets\golden\win32com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{536D528E-9360-4F28-A159-21F76458D34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E398E34F-438D-4CC8-A03A-C581515E0331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -204,9 +204,6 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -225,6 +222,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
@@ -250,7 +250,7 @@
     <tableColumn id="4" xr3:uid="{A27FC0AD-C78D-4FD1-8F51-927E6F09246C}" name="ColFormula" dataDxfId="3">
       <calculatedColumnFormula>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F1BCF14-F6A1-49D7-BDC5-54D278E411A4}" name="TestFormattedPct" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{5F1BCF14-F6A1-49D7-BDC5-54D278E411A4}" name="TestFormattedPct" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -690,13 +690,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:E6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>7</formula>
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>2</formula>
       <formula>3</formula>
     </cfRule>

--- a/tests/assets/golden/win32com/test_template_1_filled.xlsx
+++ b/tests/assets/golden/win32com/test_template_1_filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\xlfill\tests\assets\golden\win32com\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\botti\Desktop\fillxl\tests\assets\golden\win32com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC7F6658-6D69-4448-B631-5472F278CB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E398E34F-438D-4CC8-A03A-C581515E0331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,22 +186,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -221,6 +222,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
@@ -246,7 +250,7 @@
     <tableColumn id="4" xr3:uid="{A27FC0AD-C78D-4FD1-8F51-927E6F09246C}" name="ColFormula" dataDxfId="3">
       <calculatedColumnFormula>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{5F1BCF14-F6A1-49D7-BDC5-54D278E411A4}" name="TestFormattedPct" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{5F1BCF14-F6A1-49D7-BDC5-54D278E411A4}" name="TestFormattedPct" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -523,7 +527,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -545,14 +549,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -590,92 +594,92 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>0.12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>0.34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B5">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>0.78</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="e">
         <f>TableTest[[#This Row],[Col1]]+TableTest[[#This Row],[Col2]]</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>0.9</v>
       </c>
     </row>
@@ -686,13 +690,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:E6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>7</formula>
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>2</formula>
       <formula>3</formula>
     </cfRule>
@@ -747,7 +751,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
